--- a/workbook/Product_Costing_Vendor_Sourcing.xlsx
+++ b/workbook/Product_Costing_Vendor_Sourcing.xlsx
@@ -905,7 +905,6 @@
       </c>
       <c r="B2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -917,15 +916,12 @@
       </c>
       <c r="E2">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F2" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G2" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
       <c r="I2" s="5" t="n">
         <v>1</v>
@@ -939,7 +935,6 @@
       </c>
       <c r="B3">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -951,15 +946,12 @@
       </c>
       <c r="E3">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F3" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G3" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="4">
@@ -970,7 +962,6 @@
       </c>
       <c r="B4">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -982,15 +973,12 @@
       </c>
       <c r="E4">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F4" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G4" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="5">
@@ -1001,7 +989,6 @@
       </c>
       <c r="B5">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,645 +1000,502 @@
       </c>
       <c r="E5">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F5" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G5" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="B6">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E6">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F6" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G6" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="B7">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E7">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F7" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G7" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="B8">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E8">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F8" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G8" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="B9">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E9">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F9" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G9" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="10">
       <c r="B10">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E10">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F10" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G10" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="11">
       <c r="B11">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E11">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F11" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G11" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="B12">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E12">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F12" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G12" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="B13">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E13">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F13" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G13" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="B14">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E14">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F14" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G14" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="B15">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E15">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F15" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G15" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="B16">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E16">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F16" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G16" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="17">
       <c r="B17">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E17">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F17" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G17" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="18">
       <c r="B18">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E18">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F18" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G18" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="19">
       <c r="B19">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E19">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F19" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G19" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="20">
       <c r="B20">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E20">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F20" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G20" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E21">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F21" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G21" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E22">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F22" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G22" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E23">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F23" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G23" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E24">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F24" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G24" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="25">
       <c r="B25">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E25">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F25" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G25" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="26">
       <c r="B26">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E26">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F26" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G26" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="27">
       <c r="B27">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E27">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F27" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G27" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="28">
       <c r="B28">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E28">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F28" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G28" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="29">
       <c r="B29">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E29">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F29" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G29" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="30">
       <c r="B30">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E30">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F30" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G30" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="31">
       <c r="B31">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E31">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F31" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G31" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="32">
       <c r="B32">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E32">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F32" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G32" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="33">
       <c r="B33">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E33">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F33" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G33" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="34">
       <c r="B34">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E34">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F34" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G34" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="35">
       <c r="B35">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E35">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F35" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G35" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="36">
       <c r="B36">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E36">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F36" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G36" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="37">
       <c r="B37">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E37">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F37" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G37" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="38">
       <c r="B38">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E38">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F38" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G38" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E39">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F39" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G39" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
-        <v/>
       </c>
       <c r="E40">
         <f>[@[Qty_Per_Product]]*$I$2</f>
-        <v/>
       </c>
       <c r="F40" s="2">
         <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
-        <v/>
       </c>
       <c r="G40" s="2">
         <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
-        <v/>
       </c>
     </row>
   </sheetData>

--- a/workbook/Product_Costing_Vendor_Sourcing.xlsx
+++ b/workbook/Product_Costing_Vendor_Sourcing.xlsx
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A2="","",IFNA(SWITCH($C2,"Vendor_A",XLOOKUP($A2,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A2,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A2,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -915,13 +915,13 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A2="","",$D2*$I$2)</f>
       </c>
       <c r="F2" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A2="","",IFNA(SWITCH($C2,"Vendor_A",XLOOKUP($A2,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A2,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A2,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G2" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A2="","",IF($F2="","",$E2*$F2))</f>
       </c>
       <c r="I2" s="5" t="n">
         <v>1</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A3="","",IFNA(SWITCH($C3,"Vendor_A",XLOOKUP($A3,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A3,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A3,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -945,13 +945,13 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A3="","",$D3*$I$2)</f>
       </c>
       <c r="F3" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A3="","",IFNA(SWITCH($C3,"Vendor_A",XLOOKUP($A3,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A3,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A3,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G3" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A3="","",IF($F3="","",$E3*$F3))</f>
       </c>
     </row>
     <row r="4">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A4="","",IFNA(SWITCH($C4,"Vendor_A",XLOOKUP($A4,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A4,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A4,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -972,13 +972,13 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A4="","",$D4*$I$2)</f>
       </c>
       <c r="F4" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A4="","",IFNA(SWITCH($C4,"Vendor_A",XLOOKUP($A4,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A4,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A4,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G4" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A4="","",IF($F4="","",$E4*$F4))</f>
       </c>
     </row>
     <row r="5">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A5="","",IFNA(SWITCH($C5,"Vendor_A",XLOOKUP($A5,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A5,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A5,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -999,503 +999,503 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A5="","",$D5*$I$2)</f>
       </c>
       <c r="F5" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A5="","",IFNA(SWITCH($C5,"Vendor_A",XLOOKUP($A5,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A5,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A5,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G5" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A5="","",IF($F5="","",$E5*$F5))</f>
       </c>
     </row>
     <row r="6">
       <c r="B6">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A6="","",IFNA(SWITCH($C6,"Vendor_A",XLOOKUP($A6,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A6,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A6,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E6">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A6="","",$D6*$I$2)</f>
       </c>
       <c r="F6" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A6="","",IFNA(SWITCH($C6,"Vendor_A",XLOOKUP($A6,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A6,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A6,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G6" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A6="","",IF($F6="","",$E6*$F6))</f>
       </c>
     </row>
     <row r="7">
       <c r="B7">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A7="","",IFNA(SWITCH($C7,"Vendor_A",XLOOKUP($A7,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A7,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A7,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E7">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A7="","",$D7*$I$2)</f>
       </c>
       <c r="F7" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A7="","",IFNA(SWITCH($C7,"Vendor_A",XLOOKUP($A7,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A7,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A7,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G7" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A7="","",IF($F7="","",$E7*$F7))</f>
       </c>
     </row>
     <row r="8">
       <c r="B8">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A8="","",IFNA(SWITCH($C8,"Vendor_A",XLOOKUP($A8,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A8,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A8,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E8">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A8="","",$D8*$I$2)</f>
       </c>
       <c r="F8" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A8="","",IFNA(SWITCH($C8,"Vendor_A",XLOOKUP($A8,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A8,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A8,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G8" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A8="","",IF($F8="","",$E8*$F8))</f>
       </c>
     </row>
     <row r="9">
       <c r="B9">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A9="","",IFNA(SWITCH($C9,"Vendor_A",XLOOKUP($A9,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A9,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A9,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E9">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A9="","",$D9*$I$2)</f>
       </c>
       <c r="F9" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A9="","",IFNA(SWITCH($C9,"Vendor_A",XLOOKUP($A9,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A9,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A9,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G9" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A9="","",IF($F9="","",$E9*$F9))</f>
       </c>
     </row>
     <row r="10">
       <c r="B10">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A10="","",IFNA(SWITCH($C10,"Vendor_A",XLOOKUP($A10,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A10,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A10,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E10">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A10="","",$D10*$I$2)</f>
       </c>
       <c r="F10" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A10="","",IFNA(SWITCH($C10,"Vendor_A",XLOOKUP($A10,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A10,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A10,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G10" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A10="","",IF($F10="","",$E10*$F10))</f>
       </c>
     </row>
     <row r="11">
       <c r="B11">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A11="","",IFNA(SWITCH($C11,"Vendor_A",XLOOKUP($A11,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A11,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A11,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E11">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A11="","",$D11*$I$2)</f>
       </c>
       <c r="F11" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A11="","",IFNA(SWITCH($C11,"Vendor_A",XLOOKUP($A11,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A11,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A11,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G11" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A11="","",IF($F11="","",$E11*$F11))</f>
       </c>
     </row>
     <row r="12">
       <c r="B12">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A12="","",IFNA(SWITCH($C12,"Vendor_A",XLOOKUP($A12,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A12,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A12,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E12">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A12="","",$D12*$I$2)</f>
       </c>
       <c r="F12" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A12="","",IFNA(SWITCH($C12,"Vendor_A",XLOOKUP($A12,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A12,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A12,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G12" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A12="","",IF($F12="","",$E12*$F12))</f>
       </c>
     </row>
     <row r="13">
       <c r="B13">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A13="","",IFNA(SWITCH($C13,"Vendor_A",XLOOKUP($A13,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A13,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A13,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E13">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A13="","",$D13*$I$2)</f>
       </c>
       <c r="F13" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A13="","",IFNA(SWITCH($C13,"Vendor_A",XLOOKUP($A13,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A13,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A13,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G13" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A13="","",IF($F13="","",$E13*$F13))</f>
       </c>
     </row>
     <row r="14">
       <c r="B14">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A14="","",IFNA(SWITCH($C14,"Vendor_A",XLOOKUP($A14,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A14,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A14,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E14">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A14="","",$D14*$I$2)</f>
       </c>
       <c r="F14" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A14="","",IFNA(SWITCH($C14,"Vendor_A",XLOOKUP($A14,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A14,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A14,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G14" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A14="","",IF($F14="","",$E14*$F14))</f>
       </c>
     </row>
     <row r="15">
       <c r="B15">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A15="","",IFNA(SWITCH($C15,"Vendor_A",XLOOKUP($A15,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A15,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A15,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E15">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A15="","",$D15*$I$2)</f>
       </c>
       <c r="F15" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A15="","",IFNA(SWITCH($C15,"Vendor_A",XLOOKUP($A15,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A15,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A15,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G15" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A15="","",IF($F15="","",$E15*$F15))</f>
       </c>
     </row>
     <row r="16">
       <c r="B16">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A16="","",IFNA(SWITCH($C16,"Vendor_A",XLOOKUP($A16,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A16,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A16,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E16">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A16="","",$D16*$I$2)</f>
       </c>
       <c r="F16" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A16="","",IFNA(SWITCH($C16,"Vendor_A",XLOOKUP($A16,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A16,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A16,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G16" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A16="","",IF($F16="","",$E16*$F16))</f>
       </c>
     </row>
     <row r="17">
       <c r="B17">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A17="","",IFNA(SWITCH($C17,"Vendor_A",XLOOKUP($A17,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A17,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A17,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E17">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A17="","",$D17*$I$2)</f>
       </c>
       <c r="F17" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A17="","",IFNA(SWITCH($C17,"Vendor_A",XLOOKUP($A17,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A17,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A17,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G17" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A17="","",IF($F17="","",$E17*$F17))</f>
       </c>
     </row>
     <row r="18">
       <c r="B18">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A18="","",IFNA(SWITCH($C18,"Vendor_A",XLOOKUP($A18,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A18,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A18,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E18">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A18="","",$D18*$I$2)</f>
       </c>
       <c r="F18" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A18="","",IFNA(SWITCH($C18,"Vendor_A",XLOOKUP($A18,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A18,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A18,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G18" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A18="","",IF($F18="","",$E18*$F18))</f>
       </c>
     </row>
     <row r="19">
       <c r="B19">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A19="","",IFNA(SWITCH($C19,"Vendor_A",XLOOKUP($A19,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A19,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A19,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E19">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A19="","",$D19*$I$2)</f>
       </c>
       <c r="F19" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A19="","",IFNA(SWITCH($C19,"Vendor_A",XLOOKUP($A19,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A19,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A19,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G19" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A19="","",IF($F19="","",$E19*$F19))</f>
       </c>
     </row>
     <row r="20">
       <c r="B20">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A20="","",IFNA(SWITCH($C20,"Vendor_A",XLOOKUP($A20,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A20,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A20,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E20">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A20="","",$D20*$I$2)</f>
       </c>
       <c r="F20" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A20="","",IFNA(SWITCH($C20,"Vendor_A",XLOOKUP($A20,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A20,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A20,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G20" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A20="","",IF($F20="","",$E20*$F20))</f>
       </c>
     </row>
     <row r="21">
       <c r="B21">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A21="","",IFNA(SWITCH($C21,"Vendor_A",XLOOKUP($A21,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A21,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A21,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E21">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A21="","",$D21*$I$2)</f>
       </c>
       <c r="F21" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A21="","",IFNA(SWITCH($C21,"Vendor_A",XLOOKUP($A21,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A21,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A21,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G21" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A21="","",IF($F21="","",$E21*$F21))</f>
       </c>
     </row>
     <row r="22">
       <c r="B22">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A22="","",IFNA(SWITCH($C22,"Vendor_A",XLOOKUP($A22,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A22,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A22,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E22">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A22="","",$D22*$I$2)</f>
       </c>
       <c r="F22" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A22="","",IFNA(SWITCH($C22,"Vendor_A",XLOOKUP($A22,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A22,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A22,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G22" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A22="","",IF($F22="","",$E22*$F22))</f>
       </c>
     </row>
     <row r="23">
       <c r="B23">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A23="","",IFNA(SWITCH($C23,"Vendor_A",XLOOKUP($A23,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A23,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A23,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E23">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A23="","",$D23*$I$2)</f>
       </c>
       <c r="F23" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A23="","",IFNA(SWITCH($C23,"Vendor_A",XLOOKUP($A23,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A23,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A23,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G23" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A23="","",IF($F23="","",$E23*$F23))</f>
       </c>
     </row>
     <row r="24">
       <c r="B24">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A24="","",IFNA(SWITCH($C24,"Vendor_A",XLOOKUP($A24,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A24,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A24,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E24">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A24="","",$D24*$I$2)</f>
       </c>
       <c r="F24" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A24="","",IFNA(SWITCH($C24,"Vendor_A",XLOOKUP($A24,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A24,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A24,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G24" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A24="","",IF($F24="","",$E24*$F24))</f>
       </c>
     </row>
     <row r="25">
       <c r="B25">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A25="","",IFNA(SWITCH($C25,"Vendor_A",XLOOKUP($A25,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A25,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A25,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E25">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A25="","",$D25*$I$2)</f>
       </c>
       <c r="F25" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A25="","",IFNA(SWITCH($C25,"Vendor_A",XLOOKUP($A25,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A25,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A25,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G25" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A25="","",IF($F25="","",$E25*$F25))</f>
       </c>
     </row>
     <row r="26">
       <c r="B26">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A26="","",IFNA(SWITCH($C26,"Vendor_A",XLOOKUP($A26,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A26,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A26,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E26">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A26="","",$D26*$I$2)</f>
       </c>
       <c r="F26" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A26="","",IFNA(SWITCH($C26,"Vendor_A",XLOOKUP($A26,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A26,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A26,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G26" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A26="","",IF($F26="","",$E26*$F26))</f>
       </c>
     </row>
     <row r="27">
       <c r="B27">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A27="","",IFNA(SWITCH($C27,"Vendor_A",XLOOKUP($A27,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A27,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A27,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E27">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A27="","",$D27*$I$2)</f>
       </c>
       <c r="F27" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A27="","",IFNA(SWITCH($C27,"Vendor_A",XLOOKUP($A27,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A27,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A27,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G27" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A27="","",IF($F27="","",$E27*$F27))</f>
       </c>
     </row>
     <row r="28">
       <c r="B28">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A28="","",IFNA(SWITCH($C28,"Vendor_A",XLOOKUP($A28,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A28,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A28,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E28">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A28="","",$D28*$I$2)</f>
       </c>
       <c r="F28" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A28="","",IFNA(SWITCH($C28,"Vendor_A",XLOOKUP($A28,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A28,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A28,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G28" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A28="","",IF($F28="","",$E28*$F28))</f>
       </c>
     </row>
     <row r="29">
       <c r="B29">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A29="","",IFNA(SWITCH($C29,"Vendor_A",XLOOKUP($A29,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A29,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A29,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E29">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A29="","",$D29*$I$2)</f>
       </c>
       <c r="F29" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A29="","",IFNA(SWITCH($C29,"Vendor_A",XLOOKUP($A29,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A29,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A29,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G29" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A29="","",IF($F29="","",$E29*$F29))</f>
       </c>
     </row>
     <row r="30">
       <c r="B30">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A30="","",IFNA(SWITCH($C30,"Vendor_A",XLOOKUP($A30,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A30,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A30,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E30">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A30="","",$D30*$I$2)</f>
       </c>
       <c r="F30" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A30="","",IFNA(SWITCH($C30,"Vendor_A",XLOOKUP($A30,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A30,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A30,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G30" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A30="","",IF($F30="","",$E30*$F30))</f>
       </c>
     </row>
     <row r="31">
       <c r="B31">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A31="","",IFNA(SWITCH($C31,"Vendor_A",XLOOKUP($A31,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A31,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A31,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E31">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A31="","",$D31*$I$2)</f>
       </c>
       <c r="F31" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A31="","",IFNA(SWITCH($C31,"Vendor_A",XLOOKUP($A31,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A31,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A31,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G31" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A31="","",IF($F31="","",$E31*$F31))</f>
       </c>
     </row>
     <row r="32">
       <c r="B32">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A32="","",IFNA(SWITCH($C32,"Vendor_A",XLOOKUP($A32,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A32,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A32,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E32">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A32="","",$D32*$I$2)</f>
       </c>
       <c r="F32" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A32="","",IFNA(SWITCH($C32,"Vendor_A",XLOOKUP($A32,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A32,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A32,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G32" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A32="","",IF($F32="","",$E32*$F32))</f>
       </c>
     </row>
     <row r="33">
       <c r="B33">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A33="","",IFNA(SWITCH($C33,"Vendor_A",XLOOKUP($A33,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A33,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A33,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E33">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A33="","",$D33*$I$2)</f>
       </c>
       <c r="F33" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A33="","",IFNA(SWITCH($C33,"Vendor_A",XLOOKUP($A33,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A33,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A33,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G33" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A33="","",IF($F33="","",$E33*$F33))</f>
       </c>
     </row>
     <row r="34">
       <c r="B34">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A34="","",IFNA(SWITCH($C34,"Vendor_A",XLOOKUP($A34,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A34,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A34,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E34">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A34="","",$D34*$I$2)</f>
       </c>
       <c r="F34" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A34="","",IFNA(SWITCH($C34,"Vendor_A",XLOOKUP($A34,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A34,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A34,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G34" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A34="","",IF($F34="","",$E34*$F34))</f>
       </c>
     </row>
     <row r="35">
       <c r="B35">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A35="","",IFNA(SWITCH($C35,"Vendor_A",XLOOKUP($A35,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A35,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A35,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E35">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A35="","",$D35*$I$2)</f>
       </c>
       <c r="F35" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A35="","",IFNA(SWITCH($C35,"Vendor_A",XLOOKUP($A35,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A35,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A35,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G35" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A35="","",IF($F35="","",$E35*$F35))</f>
       </c>
     </row>
     <row r="36">
       <c r="B36">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A36="","",IFNA(SWITCH($C36,"Vendor_A",XLOOKUP($A36,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A36,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A36,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E36">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A36="","",$D36*$I$2)</f>
       </c>
       <c r="F36" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A36="","",IFNA(SWITCH($C36,"Vendor_A",XLOOKUP($A36,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A36,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A36,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G36" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A36="","",IF($F36="","",$E36*$F36))</f>
       </c>
     </row>
     <row r="37">
       <c r="B37">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A37="","",IFNA(SWITCH($C37,"Vendor_A",XLOOKUP($A37,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A37,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A37,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E37">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A37="","",$D37*$I$2)</f>
       </c>
       <c r="F37" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A37="","",IFNA(SWITCH($C37,"Vendor_A",XLOOKUP($A37,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A37,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A37,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G37" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A37="","",IF($F37="","",$E37*$F37))</f>
       </c>
     </row>
     <row r="38">
       <c r="B38">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A38="","",IFNA(SWITCH($C38,"Vendor_A",XLOOKUP($A38,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A38,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A38,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E38">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A38="","",$D38*$I$2)</f>
       </c>
       <c r="F38" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A38="","",IFNA(SWITCH($C38,"Vendor_A",XLOOKUP($A38,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A38,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A38,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G38" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A38="","",IF($F38="","",$E38*$F38))</f>
       </c>
     </row>
     <row r="39">
       <c r="B39">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A39="","",IFNA(SWITCH($C39,"Vendor_A",XLOOKUP($A39,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A39,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A39,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E39">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A39="","",$D39*$I$2)</f>
       </c>
       <c r="F39" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A39="","",IFNA(SWITCH($C39,"Vendor_A",XLOOKUP($A39,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A39,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A39,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G39" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A39="","",IF($F39="","",$E39*$F39))</f>
       </c>
     </row>
     <row r="40">
       <c r="B40">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Part_Name]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Part_Name]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Part_Name])),"— not on vendor —"))</f>
+        <f>IF($A40="","",IFNA(SWITCH($C40,"Vendor_A",XLOOKUP($A40,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A40,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A40,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
       </c>
       <c r="E40">
-        <f>[@[Qty_Per_Product]]*$I$2</f>
+        <f>IF($A40="","",$D40*$I$2)</f>
       </c>
       <c r="F40" s="2">
-        <f>IF([@Part_ID]="","",IFNA(SWITCH([@Vendor],"Vendor_A",XLOOKUP([@Part_ID],tblVendorA[Part_ID],tblVendorA[Unit_Price]),"Vendor_B",XLOOKUP([@Part_ID],tblVendorB[Part_ID],tblVendorB[Unit_Price]),"Vendor_C",XLOOKUP([@Part_ID],tblVendorC[Part_ID],tblVendorC[Unit_Price])),""))</f>
+        <f>IF($A40="","",IFNA(SWITCH($C40,"Vendor_A",XLOOKUP($A40,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A40,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A40,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
       </c>
       <c r="G40" s="2">
-        <f>IF([@Part_ID]="","",IF([@Unit_Price]="","",[@Total_Qty]*[@Unit_Price]))</f>
+        <f>IF($A40="","",IF($F40="","",$E40*$F40))</f>
       </c>
     </row>
   </sheetData>

--- a/workbook/Product_Costing_Vendor_Sourcing.xlsx
+++ b/workbook/Product_Costing_Vendor_Sourcing.xlsx
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>IF($A2="","",IFNA(SWITCH($C2,"Vendor_A",XLOOKUP($A2,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A2,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A2,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A2="","",IF($C2="Vendor_A",IFERROR(VLOOKUP($A2,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C2="Vendor_B",IFERROR(VLOOKUP($A2,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C2="Vendor_C",IFERROR(VLOOKUP($A2,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <f>IF($A2="","",$D2*$I$2)</f>
       </c>
       <c r="F2" s="2">
-        <f>IF($A2="","",IFNA(SWITCH($C2,"Vendor_A",XLOOKUP($A2,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A2,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A2,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A2="","",IF($C2="Vendor_A",IFERROR(VLOOKUP($A2,Vendor_A!$A:$C,3,FALSE),""),IF($C2="Vendor_B",IFERROR(VLOOKUP($A2,Vendor_B!$A:$C,3,FALSE),""),IF($C2="Vendor_C",IFERROR(VLOOKUP($A2,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G2" s="2">
         <f>IF($A2="","",IF($F2="","",$E2*$F2))</f>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>IF($A3="","",IFNA(SWITCH($C3,"Vendor_A",XLOOKUP($A3,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A3,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A3,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A3="","",IF($C3="Vendor_A",IFERROR(VLOOKUP($A3,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C3="Vendor_B",IFERROR(VLOOKUP($A3,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C3="Vendor_C",IFERROR(VLOOKUP($A3,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <f>IF($A3="","",$D3*$I$2)</f>
       </c>
       <c r="F3" s="2">
-        <f>IF($A3="","",IFNA(SWITCH($C3,"Vendor_A",XLOOKUP($A3,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A3,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A3,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A3="","",IF($C3="Vendor_A",IFERROR(VLOOKUP($A3,Vendor_A!$A:$C,3,FALSE),""),IF($C3="Vendor_B",IFERROR(VLOOKUP($A3,Vendor_B!$A:$C,3,FALSE),""),IF($C3="Vendor_C",IFERROR(VLOOKUP($A3,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G3" s="2">
         <f>IF($A3="","",IF($F3="","",$E3*$F3))</f>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>IF($A4="","",IFNA(SWITCH($C4,"Vendor_A",XLOOKUP($A4,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A4,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A4,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A4="","",IF($C4="Vendor_A",IFERROR(VLOOKUP($A4,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C4="Vendor_B",IFERROR(VLOOKUP($A4,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C4="Vendor_C",IFERROR(VLOOKUP($A4,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <f>IF($A4="","",$D4*$I$2)</f>
       </c>
       <c r="F4" s="2">
-        <f>IF($A4="","",IFNA(SWITCH($C4,"Vendor_A",XLOOKUP($A4,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A4,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A4,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A4="","",IF($C4="Vendor_A",IFERROR(VLOOKUP($A4,Vendor_A!$A:$C,3,FALSE),""),IF($C4="Vendor_B",IFERROR(VLOOKUP($A4,Vendor_B!$A:$C,3,FALSE),""),IF($C4="Vendor_C",IFERROR(VLOOKUP($A4,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G4" s="2">
         <f>IF($A4="","",IF($F4="","",$E4*$F4))</f>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>IF($A5="","",IFNA(SWITCH($C5,"Vendor_A",XLOOKUP($A5,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A5,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A5,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A5="","",IF($C5="Vendor_A",IFERROR(VLOOKUP($A5,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C5="Vendor_B",IFERROR(VLOOKUP($A5,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C5="Vendor_C",IFERROR(VLOOKUP($A5,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <f>IF($A5="","",$D5*$I$2)</f>
       </c>
       <c r="F5" s="2">
-        <f>IF($A5="","",IFNA(SWITCH($C5,"Vendor_A",XLOOKUP($A5,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A5,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A5,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A5="","",IF($C5="Vendor_A",IFERROR(VLOOKUP($A5,Vendor_A!$A:$C,3,FALSE),""),IF($C5="Vendor_B",IFERROR(VLOOKUP($A5,Vendor_B!$A:$C,3,FALSE),""),IF($C5="Vendor_C",IFERROR(VLOOKUP($A5,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G5" s="2">
         <f>IF($A5="","",IF($F5="","",$E5*$F5))</f>
@@ -1010,13 +1010,13 @@
     </row>
     <row r="6">
       <c r="B6">
-        <f>IF($A6="","",IFNA(SWITCH($C6,"Vendor_A",XLOOKUP($A6,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A6,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A6,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A6="","",IF($C6="Vendor_A",IFERROR(VLOOKUP($A6,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C6="Vendor_B",IFERROR(VLOOKUP($A6,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C6="Vendor_C",IFERROR(VLOOKUP($A6,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E6">
         <f>IF($A6="","",$D6*$I$2)</f>
       </c>
       <c r="F6" s="2">
-        <f>IF($A6="","",IFNA(SWITCH($C6,"Vendor_A",XLOOKUP($A6,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A6,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A6,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A6="","",IF($C6="Vendor_A",IFERROR(VLOOKUP($A6,Vendor_A!$A:$C,3,FALSE),""),IF($C6="Vendor_B",IFERROR(VLOOKUP($A6,Vendor_B!$A:$C,3,FALSE),""),IF($C6="Vendor_C",IFERROR(VLOOKUP($A6,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G6" s="2">
         <f>IF($A6="","",IF($F6="","",$E6*$F6))</f>
@@ -1024,13 +1024,13 @@
     </row>
     <row r="7">
       <c r="B7">
-        <f>IF($A7="","",IFNA(SWITCH($C7,"Vendor_A",XLOOKUP($A7,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A7,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A7,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A7="","",IF($C7="Vendor_A",IFERROR(VLOOKUP($A7,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C7="Vendor_B",IFERROR(VLOOKUP($A7,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C7="Vendor_C",IFERROR(VLOOKUP($A7,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E7">
         <f>IF($A7="","",$D7*$I$2)</f>
       </c>
       <c r="F7" s="2">
-        <f>IF($A7="","",IFNA(SWITCH($C7,"Vendor_A",XLOOKUP($A7,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A7,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A7,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A7="","",IF($C7="Vendor_A",IFERROR(VLOOKUP($A7,Vendor_A!$A:$C,3,FALSE),""),IF($C7="Vendor_B",IFERROR(VLOOKUP($A7,Vendor_B!$A:$C,3,FALSE),""),IF($C7="Vendor_C",IFERROR(VLOOKUP($A7,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G7" s="2">
         <f>IF($A7="","",IF($F7="","",$E7*$F7))</f>
@@ -1038,13 +1038,13 @@
     </row>
     <row r="8">
       <c r="B8">
-        <f>IF($A8="","",IFNA(SWITCH($C8,"Vendor_A",XLOOKUP($A8,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A8,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A8,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A8="","",IF($C8="Vendor_A",IFERROR(VLOOKUP($A8,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C8="Vendor_B",IFERROR(VLOOKUP($A8,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C8="Vendor_C",IFERROR(VLOOKUP($A8,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E8">
         <f>IF($A8="","",$D8*$I$2)</f>
       </c>
       <c r="F8" s="2">
-        <f>IF($A8="","",IFNA(SWITCH($C8,"Vendor_A",XLOOKUP($A8,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A8,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A8,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A8="","",IF($C8="Vendor_A",IFERROR(VLOOKUP($A8,Vendor_A!$A:$C,3,FALSE),""),IF($C8="Vendor_B",IFERROR(VLOOKUP($A8,Vendor_B!$A:$C,3,FALSE),""),IF($C8="Vendor_C",IFERROR(VLOOKUP($A8,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G8" s="2">
         <f>IF($A8="","",IF($F8="","",$E8*$F8))</f>
@@ -1052,13 +1052,13 @@
     </row>
     <row r="9">
       <c r="B9">
-        <f>IF($A9="","",IFNA(SWITCH($C9,"Vendor_A",XLOOKUP($A9,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A9,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A9,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A9="","",IF($C9="Vendor_A",IFERROR(VLOOKUP($A9,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C9="Vendor_B",IFERROR(VLOOKUP($A9,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C9="Vendor_C",IFERROR(VLOOKUP($A9,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E9">
         <f>IF($A9="","",$D9*$I$2)</f>
       </c>
       <c r="F9" s="2">
-        <f>IF($A9="","",IFNA(SWITCH($C9,"Vendor_A",XLOOKUP($A9,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A9,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A9,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A9="","",IF($C9="Vendor_A",IFERROR(VLOOKUP($A9,Vendor_A!$A:$C,3,FALSE),""),IF($C9="Vendor_B",IFERROR(VLOOKUP($A9,Vendor_B!$A:$C,3,FALSE),""),IF($C9="Vendor_C",IFERROR(VLOOKUP($A9,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G9" s="2">
         <f>IF($A9="","",IF($F9="","",$E9*$F9))</f>
@@ -1066,13 +1066,13 @@
     </row>
     <row r="10">
       <c r="B10">
-        <f>IF($A10="","",IFNA(SWITCH($C10,"Vendor_A",XLOOKUP($A10,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A10,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A10,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A10="","",IF($C10="Vendor_A",IFERROR(VLOOKUP($A10,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C10="Vendor_B",IFERROR(VLOOKUP($A10,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C10="Vendor_C",IFERROR(VLOOKUP($A10,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E10">
         <f>IF($A10="","",$D10*$I$2)</f>
       </c>
       <c r="F10" s="2">
-        <f>IF($A10="","",IFNA(SWITCH($C10,"Vendor_A",XLOOKUP($A10,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A10,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A10,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A10="","",IF($C10="Vendor_A",IFERROR(VLOOKUP($A10,Vendor_A!$A:$C,3,FALSE),""),IF($C10="Vendor_B",IFERROR(VLOOKUP($A10,Vendor_B!$A:$C,3,FALSE),""),IF($C10="Vendor_C",IFERROR(VLOOKUP($A10,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G10" s="2">
         <f>IF($A10="","",IF($F10="","",$E10*$F10))</f>
@@ -1080,13 +1080,13 @@
     </row>
     <row r="11">
       <c r="B11">
-        <f>IF($A11="","",IFNA(SWITCH($C11,"Vendor_A",XLOOKUP($A11,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A11,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A11,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A11="","",IF($C11="Vendor_A",IFERROR(VLOOKUP($A11,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C11="Vendor_B",IFERROR(VLOOKUP($A11,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C11="Vendor_C",IFERROR(VLOOKUP($A11,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E11">
         <f>IF($A11="","",$D11*$I$2)</f>
       </c>
       <c r="F11" s="2">
-        <f>IF($A11="","",IFNA(SWITCH($C11,"Vendor_A",XLOOKUP($A11,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A11,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A11,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A11="","",IF($C11="Vendor_A",IFERROR(VLOOKUP($A11,Vendor_A!$A:$C,3,FALSE),""),IF($C11="Vendor_B",IFERROR(VLOOKUP($A11,Vendor_B!$A:$C,3,FALSE),""),IF($C11="Vendor_C",IFERROR(VLOOKUP($A11,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G11" s="2">
         <f>IF($A11="","",IF($F11="","",$E11*$F11))</f>
@@ -1094,13 +1094,13 @@
     </row>
     <row r="12">
       <c r="B12">
-        <f>IF($A12="","",IFNA(SWITCH($C12,"Vendor_A",XLOOKUP($A12,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A12,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A12,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A12="","",IF($C12="Vendor_A",IFERROR(VLOOKUP($A12,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C12="Vendor_B",IFERROR(VLOOKUP($A12,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C12="Vendor_C",IFERROR(VLOOKUP($A12,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E12">
         <f>IF($A12="","",$D12*$I$2)</f>
       </c>
       <c r="F12" s="2">
-        <f>IF($A12="","",IFNA(SWITCH($C12,"Vendor_A",XLOOKUP($A12,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A12,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A12,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A12="","",IF($C12="Vendor_A",IFERROR(VLOOKUP($A12,Vendor_A!$A:$C,3,FALSE),""),IF($C12="Vendor_B",IFERROR(VLOOKUP($A12,Vendor_B!$A:$C,3,FALSE),""),IF($C12="Vendor_C",IFERROR(VLOOKUP($A12,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G12" s="2">
         <f>IF($A12="","",IF($F12="","",$E12*$F12))</f>
@@ -1108,13 +1108,13 @@
     </row>
     <row r="13">
       <c r="B13">
-        <f>IF($A13="","",IFNA(SWITCH($C13,"Vendor_A",XLOOKUP($A13,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A13,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A13,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A13="","",IF($C13="Vendor_A",IFERROR(VLOOKUP($A13,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C13="Vendor_B",IFERROR(VLOOKUP($A13,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C13="Vendor_C",IFERROR(VLOOKUP($A13,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E13">
         <f>IF($A13="","",$D13*$I$2)</f>
       </c>
       <c r="F13" s="2">
-        <f>IF($A13="","",IFNA(SWITCH($C13,"Vendor_A",XLOOKUP($A13,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A13,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A13,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A13="","",IF($C13="Vendor_A",IFERROR(VLOOKUP($A13,Vendor_A!$A:$C,3,FALSE),""),IF($C13="Vendor_B",IFERROR(VLOOKUP($A13,Vendor_B!$A:$C,3,FALSE),""),IF($C13="Vendor_C",IFERROR(VLOOKUP($A13,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G13" s="2">
         <f>IF($A13="","",IF($F13="","",$E13*$F13))</f>
@@ -1122,13 +1122,13 @@
     </row>
     <row r="14">
       <c r="B14">
-        <f>IF($A14="","",IFNA(SWITCH($C14,"Vendor_A",XLOOKUP($A14,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A14,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A14,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A14="","",IF($C14="Vendor_A",IFERROR(VLOOKUP($A14,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C14="Vendor_B",IFERROR(VLOOKUP($A14,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C14="Vendor_C",IFERROR(VLOOKUP($A14,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E14">
         <f>IF($A14="","",$D14*$I$2)</f>
       </c>
       <c r="F14" s="2">
-        <f>IF($A14="","",IFNA(SWITCH($C14,"Vendor_A",XLOOKUP($A14,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A14,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A14,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A14="","",IF($C14="Vendor_A",IFERROR(VLOOKUP($A14,Vendor_A!$A:$C,3,FALSE),""),IF($C14="Vendor_B",IFERROR(VLOOKUP($A14,Vendor_B!$A:$C,3,FALSE),""),IF($C14="Vendor_C",IFERROR(VLOOKUP($A14,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G14" s="2">
         <f>IF($A14="","",IF($F14="","",$E14*$F14))</f>
@@ -1136,13 +1136,13 @@
     </row>
     <row r="15">
       <c r="B15">
-        <f>IF($A15="","",IFNA(SWITCH($C15,"Vendor_A",XLOOKUP($A15,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A15,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A15,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A15="","",IF($C15="Vendor_A",IFERROR(VLOOKUP($A15,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C15="Vendor_B",IFERROR(VLOOKUP($A15,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C15="Vendor_C",IFERROR(VLOOKUP($A15,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E15">
         <f>IF($A15="","",$D15*$I$2)</f>
       </c>
       <c r="F15" s="2">
-        <f>IF($A15="","",IFNA(SWITCH($C15,"Vendor_A",XLOOKUP($A15,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A15,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A15,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A15="","",IF($C15="Vendor_A",IFERROR(VLOOKUP($A15,Vendor_A!$A:$C,3,FALSE),""),IF($C15="Vendor_B",IFERROR(VLOOKUP($A15,Vendor_B!$A:$C,3,FALSE),""),IF($C15="Vendor_C",IFERROR(VLOOKUP($A15,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G15" s="2">
         <f>IF($A15="","",IF($F15="","",$E15*$F15))</f>
@@ -1150,13 +1150,13 @@
     </row>
     <row r="16">
       <c r="B16">
-        <f>IF($A16="","",IFNA(SWITCH($C16,"Vendor_A",XLOOKUP($A16,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A16,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A16,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A16="","",IF($C16="Vendor_A",IFERROR(VLOOKUP($A16,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C16="Vendor_B",IFERROR(VLOOKUP($A16,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C16="Vendor_C",IFERROR(VLOOKUP($A16,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E16">
         <f>IF($A16="","",$D16*$I$2)</f>
       </c>
       <c r="F16" s="2">
-        <f>IF($A16="","",IFNA(SWITCH($C16,"Vendor_A",XLOOKUP($A16,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A16,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A16,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A16="","",IF($C16="Vendor_A",IFERROR(VLOOKUP($A16,Vendor_A!$A:$C,3,FALSE),""),IF($C16="Vendor_B",IFERROR(VLOOKUP($A16,Vendor_B!$A:$C,3,FALSE),""),IF($C16="Vendor_C",IFERROR(VLOOKUP($A16,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G16" s="2">
         <f>IF($A16="","",IF($F16="","",$E16*$F16))</f>
@@ -1164,13 +1164,13 @@
     </row>
     <row r="17">
       <c r="B17">
-        <f>IF($A17="","",IFNA(SWITCH($C17,"Vendor_A",XLOOKUP($A17,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A17,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A17,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A17="","",IF($C17="Vendor_A",IFERROR(VLOOKUP($A17,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C17="Vendor_B",IFERROR(VLOOKUP($A17,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C17="Vendor_C",IFERROR(VLOOKUP($A17,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E17">
         <f>IF($A17="","",$D17*$I$2)</f>
       </c>
       <c r="F17" s="2">
-        <f>IF($A17="","",IFNA(SWITCH($C17,"Vendor_A",XLOOKUP($A17,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A17,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A17,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A17="","",IF($C17="Vendor_A",IFERROR(VLOOKUP($A17,Vendor_A!$A:$C,3,FALSE),""),IF($C17="Vendor_B",IFERROR(VLOOKUP($A17,Vendor_B!$A:$C,3,FALSE),""),IF($C17="Vendor_C",IFERROR(VLOOKUP($A17,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G17" s="2">
         <f>IF($A17="","",IF($F17="","",$E17*$F17))</f>
@@ -1178,13 +1178,13 @@
     </row>
     <row r="18">
       <c r="B18">
-        <f>IF($A18="","",IFNA(SWITCH($C18,"Vendor_A",XLOOKUP($A18,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A18,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A18,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A18="","",IF($C18="Vendor_A",IFERROR(VLOOKUP($A18,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C18="Vendor_B",IFERROR(VLOOKUP($A18,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C18="Vendor_C",IFERROR(VLOOKUP($A18,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E18">
         <f>IF($A18="","",$D18*$I$2)</f>
       </c>
       <c r="F18" s="2">
-        <f>IF($A18="","",IFNA(SWITCH($C18,"Vendor_A",XLOOKUP($A18,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A18,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A18,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A18="","",IF($C18="Vendor_A",IFERROR(VLOOKUP($A18,Vendor_A!$A:$C,3,FALSE),""),IF($C18="Vendor_B",IFERROR(VLOOKUP($A18,Vendor_B!$A:$C,3,FALSE),""),IF($C18="Vendor_C",IFERROR(VLOOKUP($A18,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G18" s="2">
         <f>IF($A18="","",IF($F18="","",$E18*$F18))</f>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="19">
       <c r="B19">
-        <f>IF($A19="","",IFNA(SWITCH($C19,"Vendor_A",XLOOKUP($A19,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A19,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A19,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A19="","",IF($C19="Vendor_A",IFERROR(VLOOKUP($A19,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C19="Vendor_B",IFERROR(VLOOKUP($A19,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C19="Vendor_C",IFERROR(VLOOKUP($A19,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E19">
         <f>IF($A19="","",$D19*$I$2)</f>
       </c>
       <c r="F19" s="2">
-        <f>IF($A19="","",IFNA(SWITCH($C19,"Vendor_A",XLOOKUP($A19,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A19,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A19,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A19="","",IF($C19="Vendor_A",IFERROR(VLOOKUP($A19,Vendor_A!$A:$C,3,FALSE),""),IF($C19="Vendor_B",IFERROR(VLOOKUP($A19,Vendor_B!$A:$C,3,FALSE),""),IF($C19="Vendor_C",IFERROR(VLOOKUP($A19,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G19" s="2">
         <f>IF($A19="","",IF($F19="","",$E19*$F19))</f>
@@ -1206,13 +1206,13 @@
     </row>
     <row r="20">
       <c r="B20">
-        <f>IF($A20="","",IFNA(SWITCH($C20,"Vendor_A",XLOOKUP($A20,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A20,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A20,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A20="","",IF($C20="Vendor_A",IFERROR(VLOOKUP($A20,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C20="Vendor_B",IFERROR(VLOOKUP($A20,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C20="Vendor_C",IFERROR(VLOOKUP($A20,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E20">
         <f>IF($A20="","",$D20*$I$2)</f>
       </c>
       <c r="F20" s="2">
-        <f>IF($A20="","",IFNA(SWITCH($C20,"Vendor_A",XLOOKUP($A20,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A20,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A20,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A20="","",IF($C20="Vendor_A",IFERROR(VLOOKUP($A20,Vendor_A!$A:$C,3,FALSE),""),IF($C20="Vendor_B",IFERROR(VLOOKUP($A20,Vendor_B!$A:$C,3,FALSE),""),IF($C20="Vendor_C",IFERROR(VLOOKUP($A20,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G20" s="2">
         <f>IF($A20="","",IF($F20="","",$E20*$F20))</f>
@@ -1220,13 +1220,13 @@
     </row>
     <row r="21">
       <c r="B21">
-        <f>IF($A21="","",IFNA(SWITCH($C21,"Vendor_A",XLOOKUP($A21,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A21,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A21,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A21="","",IF($C21="Vendor_A",IFERROR(VLOOKUP($A21,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C21="Vendor_B",IFERROR(VLOOKUP($A21,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C21="Vendor_C",IFERROR(VLOOKUP($A21,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E21">
         <f>IF($A21="","",$D21*$I$2)</f>
       </c>
       <c r="F21" s="2">
-        <f>IF($A21="","",IFNA(SWITCH($C21,"Vendor_A",XLOOKUP($A21,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A21,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A21,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A21="","",IF($C21="Vendor_A",IFERROR(VLOOKUP($A21,Vendor_A!$A:$C,3,FALSE),""),IF($C21="Vendor_B",IFERROR(VLOOKUP($A21,Vendor_B!$A:$C,3,FALSE),""),IF($C21="Vendor_C",IFERROR(VLOOKUP($A21,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G21" s="2">
         <f>IF($A21="","",IF($F21="","",$E21*$F21))</f>
@@ -1234,13 +1234,13 @@
     </row>
     <row r="22">
       <c r="B22">
-        <f>IF($A22="","",IFNA(SWITCH($C22,"Vendor_A",XLOOKUP($A22,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A22,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A22,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A22="","",IF($C22="Vendor_A",IFERROR(VLOOKUP($A22,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C22="Vendor_B",IFERROR(VLOOKUP($A22,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C22="Vendor_C",IFERROR(VLOOKUP($A22,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E22">
         <f>IF($A22="","",$D22*$I$2)</f>
       </c>
       <c r="F22" s="2">
-        <f>IF($A22="","",IFNA(SWITCH($C22,"Vendor_A",XLOOKUP($A22,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A22,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A22,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A22="","",IF($C22="Vendor_A",IFERROR(VLOOKUP($A22,Vendor_A!$A:$C,3,FALSE),""),IF($C22="Vendor_B",IFERROR(VLOOKUP($A22,Vendor_B!$A:$C,3,FALSE),""),IF($C22="Vendor_C",IFERROR(VLOOKUP($A22,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G22" s="2">
         <f>IF($A22="","",IF($F22="","",$E22*$F22))</f>
@@ -1248,13 +1248,13 @@
     </row>
     <row r="23">
       <c r="B23">
-        <f>IF($A23="","",IFNA(SWITCH($C23,"Vendor_A",XLOOKUP($A23,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A23,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A23,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A23="","",IF($C23="Vendor_A",IFERROR(VLOOKUP($A23,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C23="Vendor_B",IFERROR(VLOOKUP($A23,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C23="Vendor_C",IFERROR(VLOOKUP($A23,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E23">
         <f>IF($A23="","",$D23*$I$2)</f>
       </c>
       <c r="F23" s="2">
-        <f>IF($A23="","",IFNA(SWITCH($C23,"Vendor_A",XLOOKUP($A23,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A23,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A23,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A23="","",IF($C23="Vendor_A",IFERROR(VLOOKUP($A23,Vendor_A!$A:$C,3,FALSE),""),IF($C23="Vendor_B",IFERROR(VLOOKUP($A23,Vendor_B!$A:$C,3,FALSE),""),IF($C23="Vendor_C",IFERROR(VLOOKUP($A23,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G23" s="2">
         <f>IF($A23="","",IF($F23="","",$E23*$F23))</f>
@@ -1262,13 +1262,13 @@
     </row>
     <row r="24">
       <c r="B24">
-        <f>IF($A24="","",IFNA(SWITCH($C24,"Vendor_A",XLOOKUP($A24,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A24,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A24,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A24="","",IF($C24="Vendor_A",IFERROR(VLOOKUP($A24,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C24="Vendor_B",IFERROR(VLOOKUP($A24,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C24="Vendor_C",IFERROR(VLOOKUP($A24,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E24">
         <f>IF($A24="","",$D24*$I$2)</f>
       </c>
       <c r="F24" s="2">
-        <f>IF($A24="","",IFNA(SWITCH($C24,"Vendor_A",XLOOKUP($A24,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A24,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A24,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A24="","",IF($C24="Vendor_A",IFERROR(VLOOKUP($A24,Vendor_A!$A:$C,3,FALSE),""),IF($C24="Vendor_B",IFERROR(VLOOKUP($A24,Vendor_B!$A:$C,3,FALSE),""),IF($C24="Vendor_C",IFERROR(VLOOKUP($A24,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G24" s="2">
         <f>IF($A24="","",IF($F24="","",$E24*$F24))</f>
@@ -1276,13 +1276,13 @@
     </row>
     <row r="25">
       <c r="B25">
-        <f>IF($A25="","",IFNA(SWITCH($C25,"Vendor_A",XLOOKUP($A25,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A25,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A25,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A25="","",IF($C25="Vendor_A",IFERROR(VLOOKUP($A25,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C25="Vendor_B",IFERROR(VLOOKUP($A25,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C25="Vendor_C",IFERROR(VLOOKUP($A25,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E25">
         <f>IF($A25="","",$D25*$I$2)</f>
       </c>
       <c r="F25" s="2">
-        <f>IF($A25="","",IFNA(SWITCH($C25,"Vendor_A",XLOOKUP($A25,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A25,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A25,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A25="","",IF($C25="Vendor_A",IFERROR(VLOOKUP($A25,Vendor_A!$A:$C,3,FALSE),""),IF($C25="Vendor_B",IFERROR(VLOOKUP($A25,Vendor_B!$A:$C,3,FALSE),""),IF($C25="Vendor_C",IFERROR(VLOOKUP($A25,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G25" s="2">
         <f>IF($A25="","",IF($F25="","",$E25*$F25))</f>
@@ -1290,13 +1290,13 @@
     </row>
     <row r="26">
       <c r="B26">
-        <f>IF($A26="","",IFNA(SWITCH($C26,"Vendor_A",XLOOKUP($A26,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A26,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A26,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A26="","",IF($C26="Vendor_A",IFERROR(VLOOKUP($A26,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C26="Vendor_B",IFERROR(VLOOKUP($A26,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C26="Vendor_C",IFERROR(VLOOKUP($A26,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E26">
         <f>IF($A26="","",$D26*$I$2)</f>
       </c>
       <c r="F26" s="2">
-        <f>IF($A26="","",IFNA(SWITCH($C26,"Vendor_A",XLOOKUP($A26,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A26,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A26,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A26="","",IF($C26="Vendor_A",IFERROR(VLOOKUP($A26,Vendor_A!$A:$C,3,FALSE),""),IF($C26="Vendor_B",IFERROR(VLOOKUP($A26,Vendor_B!$A:$C,3,FALSE),""),IF($C26="Vendor_C",IFERROR(VLOOKUP($A26,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G26" s="2">
         <f>IF($A26="","",IF($F26="","",$E26*$F26))</f>
@@ -1304,13 +1304,13 @@
     </row>
     <row r="27">
       <c r="B27">
-        <f>IF($A27="","",IFNA(SWITCH($C27,"Vendor_A",XLOOKUP($A27,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A27,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A27,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A27="","",IF($C27="Vendor_A",IFERROR(VLOOKUP($A27,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C27="Vendor_B",IFERROR(VLOOKUP($A27,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C27="Vendor_C",IFERROR(VLOOKUP($A27,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E27">
         <f>IF($A27="","",$D27*$I$2)</f>
       </c>
       <c r="F27" s="2">
-        <f>IF($A27="","",IFNA(SWITCH($C27,"Vendor_A",XLOOKUP($A27,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A27,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A27,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A27="","",IF($C27="Vendor_A",IFERROR(VLOOKUP($A27,Vendor_A!$A:$C,3,FALSE),""),IF($C27="Vendor_B",IFERROR(VLOOKUP($A27,Vendor_B!$A:$C,3,FALSE),""),IF($C27="Vendor_C",IFERROR(VLOOKUP($A27,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G27" s="2">
         <f>IF($A27="","",IF($F27="","",$E27*$F27))</f>
@@ -1318,13 +1318,13 @@
     </row>
     <row r="28">
       <c r="B28">
-        <f>IF($A28="","",IFNA(SWITCH($C28,"Vendor_A",XLOOKUP($A28,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A28,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A28,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A28="","",IF($C28="Vendor_A",IFERROR(VLOOKUP($A28,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C28="Vendor_B",IFERROR(VLOOKUP($A28,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C28="Vendor_C",IFERROR(VLOOKUP($A28,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E28">
         <f>IF($A28="","",$D28*$I$2)</f>
       </c>
       <c r="F28" s="2">
-        <f>IF($A28="","",IFNA(SWITCH($C28,"Vendor_A",XLOOKUP($A28,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A28,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A28,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A28="","",IF($C28="Vendor_A",IFERROR(VLOOKUP($A28,Vendor_A!$A:$C,3,FALSE),""),IF($C28="Vendor_B",IFERROR(VLOOKUP($A28,Vendor_B!$A:$C,3,FALSE),""),IF($C28="Vendor_C",IFERROR(VLOOKUP($A28,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G28" s="2">
         <f>IF($A28="","",IF($F28="","",$E28*$F28))</f>
@@ -1332,13 +1332,13 @@
     </row>
     <row r="29">
       <c r="B29">
-        <f>IF($A29="","",IFNA(SWITCH($C29,"Vendor_A",XLOOKUP($A29,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A29,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A29,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A29="","",IF($C29="Vendor_A",IFERROR(VLOOKUP($A29,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C29="Vendor_B",IFERROR(VLOOKUP($A29,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C29="Vendor_C",IFERROR(VLOOKUP($A29,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E29">
         <f>IF($A29="","",$D29*$I$2)</f>
       </c>
       <c r="F29" s="2">
-        <f>IF($A29="","",IFNA(SWITCH($C29,"Vendor_A",XLOOKUP($A29,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A29,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A29,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A29="","",IF($C29="Vendor_A",IFERROR(VLOOKUP($A29,Vendor_A!$A:$C,3,FALSE),""),IF($C29="Vendor_B",IFERROR(VLOOKUP($A29,Vendor_B!$A:$C,3,FALSE),""),IF($C29="Vendor_C",IFERROR(VLOOKUP($A29,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G29" s="2">
         <f>IF($A29="","",IF($F29="","",$E29*$F29))</f>
@@ -1346,13 +1346,13 @@
     </row>
     <row r="30">
       <c r="B30">
-        <f>IF($A30="","",IFNA(SWITCH($C30,"Vendor_A",XLOOKUP($A30,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A30,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A30,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A30="","",IF($C30="Vendor_A",IFERROR(VLOOKUP($A30,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C30="Vendor_B",IFERROR(VLOOKUP($A30,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C30="Vendor_C",IFERROR(VLOOKUP($A30,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E30">
         <f>IF($A30="","",$D30*$I$2)</f>
       </c>
       <c r="F30" s="2">
-        <f>IF($A30="","",IFNA(SWITCH($C30,"Vendor_A",XLOOKUP($A30,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A30,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A30,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A30="","",IF($C30="Vendor_A",IFERROR(VLOOKUP($A30,Vendor_A!$A:$C,3,FALSE),""),IF($C30="Vendor_B",IFERROR(VLOOKUP($A30,Vendor_B!$A:$C,3,FALSE),""),IF($C30="Vendor_C",IFERROR(VLOOKUP($A30,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G30" s="2">
         <f>IF($A30="","",IF($F30="","",$E30*$F30))</f>
@@ -1360,13 +1360,13 @@
     </row>
     <row r="31">
       <c r="B31">
-        <f>IF($A31="","",IFNA(SWITCH($C31,"Vendor_A",XLOOKUP($A31,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A31,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A31,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A31="","",IF($C31="Vendor_A",IFERROR(VLOOKUP($A31,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C31="Vendor_B",IFERROR(VLOOKUP($A31,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C31="Vendor_C",IFERROR(VLOOKUP($A31,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E31">
         <f>IF($A31="","",$D31*$I$2)</f>
       </c>
       <c r="F31" s="2">
-        <f>IF($A31="","",IFNA(SWITCH($C31,"Vendor_A",XLOOKUP($A31,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A31,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A31,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A31="","",IF($C31="Vendor_A",IFERROR(VLOOKUP($A31,Vendor_A!$A:$C,3,FALSE),""),IF($C31="Vendor_B",IFERROR(VLOOKUP($A31,Vendor_B!$A:$C,3,FALSE),""),IF($C31="Vendor_C",IFERROR(VLOOKUP($A31,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G31" s="2">
         <f>IF($A31="","",IF($F31="","",$E31*$F31))</f>
@@ -1374,13 +1374,13 @@
     </row>
     <row r="32">
       <c r="B32">
-        <f>IF($A32="","",IFNA(SWITCH($C32,"Vendor_A",XLOOKUP($A32,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A32,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A32,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A32="","",IF($C32="Vendor_A",IFERROR(VLOOKUP($A32,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C32="Vendor_B",IFERROR(VLOOKUP($A32,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C32="Vendor_C",IFERROR(VLOOKUP($A32,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E32">
         <f>IF($A32="","",$D32*$I$2)</f>
       </c>
       <c r="F32" s="2">
-        <f>IF($A32="","",IFNA(SWITCH($C32,"Vendor_A",XLOOKUP($A32,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A32,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A32,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A32="","",IF($C32="Vendor_A",IFERROR(VLOOKUP($A32,Vendor_A!$A:$C,3,FALSE),""),IF($C32="Vendor_B",IFERROR(VLOOKUP($A32,Vendor_B!$A:$C,3,FALSE),""),IF($C32="Vendor_C",IFERROR(VLOOKUP($A32,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G32" s="2">
         <f>IF($A32="","",IF($F32="","",$E32*$F32))</f>
@@ -1388,13 +1388,13 @@
     </row>
     <row r="33">
       <c r="B33">
-        <f>IF($A33="","",IFNA(SWITCH($C33,"Vendor_A",XLOOKUP($A33,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A33,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A33,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A33="","",IF($C33="Vendor_A",IFERROR(VLOOKUP($A33,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C33="Vendor_B",IFERROR(VLOOKUP($A33,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C33="Vendor_C",IFERROR(VLOOKUP($A33,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E33">
         <f>IF($A33="","",$D33*$I$2)</f>
       </c>
       <c r="F33" s="2">
-        <f>IF($A33="","",IFNA(SWITCH($C33,"Vendor_A",XLOOKUP($A33,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A33,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A33,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A33="","",IF($C33="Vendor_A",IFERROR(VLOOKUP($A33,Vendor_A!$A:$C,3,FALSE),""),IF($C33="Vendor_B",IFERROR(VLOOKUP($A33,Vendor_B!$A:$C,3,FALSE),""),IF($C33="Vendor_C",IFERROR(VLOOKUP($A33,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G33" s="2">
         <f>IF($A33="","",IF($F33="","",$E33*$F33))</f>
@@ -1402,13 +1402,13 @@
     </row>
     <row r="34">
       <c r="B34">
-        <f>IF($A34="","",IFNA(SWITCH($C34,"Vendor_A",XLOOKUP($A34,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A34,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A34,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A34="","",IF($C34="Vendor_A",IFERROR(VLOOKUP($A34,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C34="Vendor_B",IFERROR(VLOOKUP($A34,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C34="Vendor_C",IFERROR(VLOOKUP($A34,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E34">
         <f>IF($A34="","",$D34*$I$2)</f>
       </c>
       <c r="F34" s="2">
-        <f>IF($A34="","",IFNA(SWITCH($C34,"Vendor_A",XLOOKUP($A34,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A34,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A34,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A34="","",IF($C34="Vendor_A",IFERROR(VLOOKUP($A34,Vendor_A!$A:$C,3,FALSE),""),IF($C34="Vendor_B",IFERROR(VLOOKUP($A34,Vendor_B!$A:$C,3,FALSE),""),IF($C34="Vendor_C",IFERROR(VLOOKUP($A34,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G34" s="2">
         <f>IF($A34="","",IF($F34="","",$E34*$F34))</f>
@@ -1416,13 +1416,13 @@
     </row>
     <row r="35">
       <c r="B35">
-        <f>IF($A35="","",IFNA(SWITCH($C35,"Vendor_A",XLOOKUP($A35,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A35,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A35,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A35="","",IF($C35="Vendor_A",IFERROR(VLOOKUP($A35,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C35="Vendor_B",IFERROR(VLOOKUP($A35,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C35="Vendor_C",IFERROR(VLOOKUP($A35,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E35">
         <f>IF($A35="","",$D35*$I$2)</f>
       </c>
       <c r="F35" s="2">
-        <f>IF($A35="","",IFNA(SWITCH($C35,"Vendor_A",XLOOKUP($A35,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A35,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A35,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A35="","",IF($C35="Vendor_A",IFERROR(VLOOKUP($A35,Vendor_A!$A:$C,3,FALSE),""),IF($C35="Vendor_B",IFERROR(VLOOKUP($A35,Vendor_B!$A:$C,3,FALSE),""),IF($C35="Vendor_C",IFERROR(VLOOKUP($A35,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G35" s="2">
         <f>IF($A35="","",IF($F35="","",$E35*$F35))</f>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="36">
       <c r="B36">
-        <f>IF($A36="","",IFNA(SWITCH($C36,"Vendor_A",XLOOKUP($A36,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A36,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A36,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A36="","",IF($C36="Vendor_A",IFERROR(VLOOKUP($A36,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C36="Vendor_B",IFERROR(VLOOKUP($A36,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C36="Vendor_C",IFERROR(VLOOKUP($A36,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E36">
         <f>IF($A36="","",$D36*$I$2)</f>
       </c>
       <c r="F36" s="2">
-        <f>IF($A36="","",IFNA(SWITCH($C36,"Vendor_A",XLOOKUP($A36,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A36,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A36,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A36="","",IF($C36="Vendor_A",IFERROR(VLOOKUP($A36,Vendor_A!$A:$C,3,FALSE),""),IF($C36="Vendor_B",IFERROR(VLOOKUP($A36,Vendor_B!$A:$C,3,FALSE),""),IF($C36="Vendor_C",IFERROR(VLOOKUP($A36,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G36" s="2">
         <f>IF($A36="","",IF($F36="","",$E36*$F36))</f>
@@ -1444,13 +1444,13 @@
     </row>
     <row r="37">
       <c r="B37">
-        <f>IF($A37="","",IFNA(SWITCH($C37,"Vendor_A",XLOOKUP($A37,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A37,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A37,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A37="","",IF($C37="Vendor_A",IFERROR(VLOOKUP($A37,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C37="Vendor_B",IFERROR(VLOOKUP($A37,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C37="Vendor_C",IFERROR(VLOOKUP($A37,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E37">
         <f>IF($A37="","",$D37*$I$2)</f>
       </c>
       <c r="F37" s="2">
-        <f>IF($A37="","",IFNA(SWITCH($C37,"Vendor_A",XLOOKUP($A37,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A37,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A37,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A37="","",IF($C37="Vendor_A",IFERROR(VLOOKUP($A37,Vendor_A!$A:$C,3,FALSE),""),IF($C37="Vendor_B",IFERROR(VLOOKUP($A37,Vendor_B!$A:$C,3,FALSE),""),IF($C37="Vendor_C",IFERROR(VLOOKUP($A37,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G37" s="2">
         <f>IF($A37="","",IF($F37="","",$E37*$F37))</f>
@@ -1458,13 +1458,13 @@
     </row>
     <row r="38">
       <c r="B38">
-        <f>IF($A38="","",IFNA(SWITCH($C38,"Vendor_A",XLOOKUP($A38,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A38,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A38,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A38="","",IF($C38="Vendor_A",IFERROR(VLOOKUP($A38,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C38="Vendor_B",IFERROR(VLOOKUP($A38,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C38="Vendor_C",IFERROR(VLOOKUP($A38,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E38">
         <f>IF($A38="","",$D38*$I$2)</f>
       </c>
       <c r="F38" s="2">
-        <f>IF($A38="","",IFNA(SWITCH($C38,"Vendor_A",XLOOKUP($A38,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A38,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A38,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A38="","",IF($C38="Vendor_A",IFERROR(VLOOKUP($A38,Vendor_A!$A:$C,3,FALSE),""),IF($C38="Vendor_B",IFERROR(VLOOKUP($A38,Vendor_B!$A:$C,3,FALSE),""),IF($C38="Vendor_C",IFERROR(VLOOKUP($A38,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G38" s="2">
         <f>IF($A38="","",IF($F38="","",$E38*$F38))</f>
@@ -1472,13 +1472,13 @@
     </row>
     <row r="39">
       <c r="B39">
-        <f>IF($A39="","",IFNA(SWITCH($C39,"Vendor_A",XLOOKUP($A39,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A39,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A39,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A39="","",IF($C39="Vendor_A",IFERROR(VLOOKUP($A39,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C39="Vendor_B",IFERROR(VLOOKUP($A39,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C39="Vendor_C",IFERROR(VLOOKUP($A39,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E39">
         <f>IF($A39="","",$D39*$I$2)</f>
       </c>
       <c r="F39" s="2">
-        <f>IF($A39="","",IFNA(SWITCH($C39,"Vendor_A",XLOOKUP($A39,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A39,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A39,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A39="","",IF($C39="Vendor_A",IFERROR(VLOOKUP($A39,Vendor_A!$A:$C,3,FALSE),""),IF($C39="Vendor_B",IFERROR(VLOOKUP($A39,Vendor_B!$A:$C,3,FALSE),""),IF($C39="Vendor_C",IFERROR(VLOOKUP($A39,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G39" s="2">
         <f>IF($A39="","",IF($F39="","",$E39*$F39))</f>
@@ -1486,13 +1486,13 @@
     </row>
     <row r="40">
       <c r="B40">
-        <f>IF($A40="","",IFNA(SWITCH($C40,"Vendor_A",XLOOKUP($A40,Vendor_A!$A:$A,Vendor_A!$B:$B),"Vendor_B",XLOOKUP($A40,Vendor_B!$A:$A,Vendor_B!$B:$B),"Vendor_C",XLOOKUP($A40,Vendor_C!$A:$A,Vendor_C!$B:$B)),"-- not on vendor --"))</f>
+        <f>IF($A40="","",IF($C40="Vendor_A",IFERROR(VLOOKUP($A40,Vendor_A!$A:$C,2,FALSE),"-- not on vendor --"),IF($C40="Vendor_B",IFERROR(VLOOKUP($A40,Vendor_B!$A:$C,2,FALSE),"-- not on vendor --"),IF($C40="Vendor_C",IFERROR(VLOOKUP($A40,Vendor_C!$A:$C,2,FALSE),"-- not on vendor --"),"-- not on vendor --"))))</f>
       </c>
       <c r="E40">
         <f>IF($A40="","",$D40*$I$2)</f>
       </c>
       <c r="F40" s="2">
-        <f>IF($A40="","",IFNA(SWITCH($C40,"Vendor_A",XLOOKUP($A40,Vendor_A!$A:$A,Vendor_A!$C:$C),"Vendor_B",XLOOKUP($A40,Vendor_B!$A:$A,Vendor_B!$C:$C),"Vendor_C",XLOOKUP($A40,Vendor_C!$A:$A,Vendor_C!$C:$C)),""))</f>
+        <f>IF($A40="","",IF($C40="Vendor_A",IFERROR(VLOOKUP($A40,Vendor_A!$A:$C,3,FALSE),""),IF($C40="Vendor_B",IFERROR(VLOOKUP($A40,Vendor_B!$A:$C,3,FALSE),""),IF($C40="Vendor_C",IFERROR(VLOOKUP($A40,Vendor_C!$A:$C,3,FALSE),""),""))))</f>
       </c>
       <c r="G40" s="2">
         <f>IF($A40="","",IF($F40="","",$E40*$F40))</f>
